--- a/fEstacionamento.xlsx
+++ b/fEstacionamento.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/BI_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/dash-ticket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{CD5BA575-D864-43BF-89B6-A8B4B7960132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A39B020F-6019-4F59-9B59-B45833943908}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{CD5BA575-D864-43BF-89B6-A8B4B7960132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9439A926-4867-4128-9847-A2209A23E998}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{356E8128-3B93-43A7-AF35-DA55300C4A68}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="71">
   <si>
     <t>par-5</t>
   </si>
@@ -213,6 +213,45 @@
   </si>
   <si>
     <t>2025.08.14-CAMLI5-OITAVAS</t>
+  </si>
+  <si>
+    <t>2026.01.21-CAMCA4-3</t>
+  </si>
+  <si>
+    <t>2026.01.24-CAMCA4-4</t>
+  </si>
+  <si>
+    <t>2026.01.29-CAMBR2-1</t>
+  </si>
+  <si>
+    <t>2026.02.01-CAMCA4-5</t>
+  </si>
+  <si>
+    <t>2026.02.15-CAMCA4-Quartas</t>
+  </si>
+  <si>
+    <t>2026.02.25-CAMLI5-2° FASE</t>
+  </si>
+  <si>
+    <t>2026.02.28-CAMCA4-SEMIS - TR</t>
+  </si>
+  <si>
+    <t>2026.03.07-CAMCA4-FINAL - TR</t>
+  </si>
+  <si>
+    <t>2026.03.10-CAMLI5-3° Fase</t>
+  </si>
+  <si>
+    <t>2026.03.14-CAMBR2-6</t>
+  </si>
+  <si>
+    <t>2026.04.01-CAMBR2-9</t>
+  </si>
+  <si>
+    <t>2026.04.09-CAMSU6-FG</t>
+  </si>
+  <si>
+    <t>2026.04.12-CAMBR2-11</t>
   </si>
 </sst>
 </file>
@@ -618,12 +657,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90EB12ED-B121-4FC4-BA8B-637539FB73F7}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -1231,6 +1270,140 @@
         <v>31280.900699999995</v>
       </c>
     </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" s="4">
+        <v>9340</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>59</v>
+      </c>
+      <c r="C57" s="4">
+        <v>7970</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="4">
+        <v>21340</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>61</v>
+      </c>
+      <c r="C59" s="4">
+        <v>13440</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" s="4">
+        <v>7010</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" s="4">
+        <v>38590</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" t="s">
+        <v>64</v>
+      </c>
+      <c r="C62" s="4">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" t="s">
+        <v>65</v>
+      </c>
+      <c r="C63" s="4">
+        <v>6190</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" s="4">
+        <v>48760</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" s="4">
+        <v>15670</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B68" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{90EB12ED-B121-4FC4-BA8B-637539FB73F7}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
